--- a/SMTinel_Yokoten_Knowledge_DB.xlsx
+++ b/SMTinel_Yokoten_Knowledge_DB.xlsx
@@ -11,14 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical Characteristics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Cross Reference" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Qualification'!$A$1:$O$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$Q$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$M$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Critical Characteristics'!$A$1:$M$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Instructions'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Critical Characteristics'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Component Cross Reference'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Instructions'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -29,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +46,12 @@
     <font>
       <b val="1"/>
       <color rgb="0033472D"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -88,6 +96,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -191,7 +208,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TblFindings" displayName="TblFindings" ref="A1:O10" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TblFindings" displayName="TblFindings" ref="A1:Q10" headerRowCount="1">
   <autoFilter ref="A1:O3"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Finding ID"/>
@@ -237,7 +254,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TblCriticalCharacteristics" displayName="TblCriticalCharacteristics" ref="A1:M9" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TblCriticalCharacteristics" displayName="TblCriticalCharacteristics" ref="A1:N9" headerRowCount="1">
   <autoFilter ref="A1:M2"/>
   <tableColumns count="13">
     <tableColumn id="1" name="CC ID"/>
@@ -253,6 +270,27 @@
     <tableColumn id="11" name="Source"/>
     <tableColumn id="12" name="Owner"/>
     <tableColumn id="13" name="Active"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TblComponentCrossReference" displayName="TblComponentCrossReference" ref="A1:L6" headerRowCount="1">
+  <autoFilter ref="A1:L6"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Mapping ID"/>
+    <tableColumn id="2" name="Component CPN"/>
+    <tableColumn id="3" name="Product"/>
+    <tableColumn id="4" name="Board Part Number"/>
+    <tableColumn id="5" name="Rev"/>
+    <tableColumn id="6" name="RefDes"/>
+    <tableColumn id="7" name="Side"/>
+    <tableColumn id="8" name="MPN"/>
+    <tableColumn id="9" name="Description"/>
+    <tableColumn id="10" name="Source"/>
+    <tableColumn id="11" name="Notes"/>
+    <tableColumn id="12" name="Active"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -765,24 +803,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -808,55 +848,65 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Component CPN</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RefDes</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Rev</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Finding</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Critical Characteristic</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Migration Gate</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>8D / LL Link</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -883,42 +933,52 @@
           <t>73-103603-05</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>27-100137-01</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>J73</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>J73 reverse orientation - customer complaint history</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>J73 orientation</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>P&amp;P orientation verification + AOI body/orientation challenge + first-piece verification before line release.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Customer complaint / 8D lesson learned</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
@@ -946,48 +1006,58 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>27-100137-01</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>J73</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>B0</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>L13</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>AOI orientation coverage gap during line qualification</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>J73 orientation</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Verify AOI library discrimination for reverse orientation and challenge the critical orientation during requalification.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Historical line finding</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
@@ -1015,43 +1085,45 @@
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>WO identity/revision mismatch: released B0 product was scheduled with an incorrect revision and a separate WO used an incorrect product PN.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>WO Product PN + released revision identity</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>System must validate requested Product PN and released revision before WO creation/release; confirm model/PN/revision on first piece before production release.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Tracker_Control_Cambios_2026-09-15_Taylor_RCCA.xlsx · EVT-08 / EVT-09</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Planeación / PM</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1080,43 +1152,45 @@
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>BOM consolidation produced PN / RefDes / quantity discrepancies against the SMT Load List and required the lists to be regenerated.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Released BOM-to-Load-List reconciliation</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Automatically compare PN, RefDes, Qty and revision against the released BOM before the Load List is approved or released.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Tracker_Control_Cambios_2026-09-15_Taylor_RCCA.xlsx · EVT-01</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Programación / Calidad</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1143,49 +1217,51 @@
           <t>74-133408-02</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>B0</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>The 74-PN alone did not uniquely define the ODM build configuration; U58 plus the applicable revision and change implementation had to remain aligned across SMT and ICT.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Configuration identity = U58 + applicable revision + released change set</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Bind WO to U58 + revision + applicable ECN/EA/route; confirm SMT and ICT configuration in a pre-release checklist, including impacted RefDes/tests.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Tracker_Control_Cambios_2026-09-15_Taylor_RCCA.xlsx · EVT-02 / EVT-03 / EVT-04</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Planeación / Producto / SMT / ICT</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1210,43 +1286,45 @@
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Component-to-component contact / insufficient clearance was observed in dense capacitor zones across multiple Taylor builds. AOI did not provide robust minimum-gap coverage, and material body envelope plus placement must be controlled together.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Minimum component-to-component clearance / approved body envelope in dense capacitor zones</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Validate AVL/body dimensions, P&amp;P package/centering/XY/theta and post-placement/post-reflow gap before release; revalidate when supplier/MPN/body envelope or P&amp;P package changes.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Tracker_Control_Cambios_2026-09-15_Taylor_RCCA.xlsx · EVT-19 / EVT-20 / EVT-21; Taylor RCCA project record</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Carlos Martínez / Josué Rangel / José Cruz</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1271,43 +1349,45 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Microphone lifting / lateral solder-ball displacement was associated with the seating condition and excessive placement pressure risk; NIXIE uses a flat seating surface and requires controlled nozzle and P&amp;P settings.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Microphone seating pressure / solder-ball integrity</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Use approved Universal Fuzion nozzle, Part Data and P&amp;P settings per supplier datasheet; validate post-placement and post-reflow during safe launch; supplier/nozzle changes require revalidation.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>SMTinel project record · NIXIE Q1WK08 / WK10 safe launch</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>SMT-P&amp;P / Carlos Martínez</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1334,42 +1414,52 @@
           <t>73-20247-06</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15-102981-01; 15-102981-02</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>A deviation intended for CRBU could remove the material qualification block globally by PN, allowing Cancelled Toshiba material to be used in NGFWBU where the deviation did not apply.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Material qualification / deviation applicability for U23 15-102981-01 → 15-102981-02</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Deviation override must be validated by BU + SKU/family + WO before bypassing the SAP qualification block; a scope mismatch must remain blocked.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>SMTinel project record · CRBU vs NGFWBU Cancelled/IPQ deviation analysis</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
@@ -1395,48 +1485,58 @@
           <t>73-20249-06</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15-102981-01; 15-102981-02</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>A deviation intended for CRBU could remove the material qualification block globally by PN, allowing Cancelled Toshiba material to be used in NGFWBU where the deviation did not apply.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Material qualification / deviation applicability for U23 15-102981-01 → 15-102981-02</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Deviation override must be validated by BU + SKU/family + WO before bypassing the SAP qualification block; a scope mismatch must remain blocked.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>SMTinel project record · CRBU vs NGFWBU Cancelled/IPQ deviation analysis</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:Q10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2474,7 +2574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2483,13 +2583,14 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2525,35 +2626,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Component CPN</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>RefDes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Characteristic</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Control / Detection</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Migration Requirement</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -2584,35 +2690,40 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>27-100137-01</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>J73</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Connector orientation</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>P&amp;P orientation verification + AOI body/orientation feature</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Repeat critical orientation challenge on every new line or requalification.</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Customer complaint / lesson learned</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Josué Rangel / Alberto Cruz / Carlos Martínez</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2641,37 +2752,38 @@
       </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>WO / First Piece</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Product PN and released revision identity</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>System validation of Product PN + released revision at WO create/release plus first-piece identity confirmation</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Reject or hold WO when PN/revision does not match the released configuration; reconcile before production.</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Configuration control tracker · EVT-08 / EVT-09</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Planeación / PM</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2700,37 +2812,38 @@
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>BOM / Load List</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>PN / RefDes / Qty / revision reconciliation</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Automatic BOM vs Load List comparison before release</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Load List cannot be released with PN, RefDes, Qty or revision mismatch against released BOM.</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Configuration control tracker · EVT-01</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Programación / Calidad</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2763,37 +2876,38 @@
         </is>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>U58 / impacted RefDes</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>ODM configuration identity and change implementation</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>WO binds U58 + revision + change document; SMT/ICT checklist verifies physical configuration and impacted tests</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Requalify/reverify the configuration whenever U58/revision or impacted RefDes/test content changes.</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Configuration control tracker · EVT-02 / EVT-03 / EVT-04</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Planeación / Producto / SMT / ICT</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2818,37 +2932,38 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>C69_B/C4_B; C267/C268; C280/C282/C283/C284/C274/C67/C70</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Minimum body-to-body clearance / approved component body envelope</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>AVL dimensional review + P&amp;P Debug Mode/placement verification + post-placement/post-reflow gap inspection; AOI or alternate visual control</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Revalidate when supplier/MPN/body envelope, nozzle/package or P&amp;P placement definition changes in a critical zone.</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Taylor RCCA / SMTinel project record</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Carlos Martínez / Josué Rangel / José Cruz</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2873,37 +2988,38 @@
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Microphone</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Seating pressure / solder-ball integrity</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Approved Universal Fuzion nozzle and Part Data/settings per supplier datasheet plus post-placement/post-reflow verification</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Revalidate nozzle/settings and safe-launch condition whenever supplier or placement definition changes.</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>NIXIE Q1WK08 / WK10 safe-launch project record</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>SMT-P&amp;P / Carlos Martínez</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2934,31 +3050,36 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>15-102981-01; 15-102981-02</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>U23</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Material qualification and deviation scope for 15-102981-01 → 15-102981-02</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Traceability scan → SAP qualification check → deviation scope check by BU + SKU/family + WO → allow/block</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>A deviation must never globally override Cancelled/IPQ status outside its approved product/BU/WO scope.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>CRBU vs NGFWBU deviation analysis</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2989,38 +3110,43 @@
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>15-102981-01; 15-102981-02</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>U23</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Material qualification and deviation scope for 15-102981-01 → 15-102981-02</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Traceability scan → SAP qualification check → deviation scope check by BU + SKU/family + WO → allow/block</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>A deviation must never globally override Cancelled/IPQ status outside its approved product/BU/WO scope.</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>CRBU vs NGFWBU deviation analysis</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3034,7 +3160,351 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Mapping ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Component CPN</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Board Part Number</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>RefDes</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>MPN</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>MAP-PICTORIS-J73</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>27-100137-01</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>PICTORIS</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>73-103603-05</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>J73</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr"/>
+      <c r="H2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>J73 orientation-controlled connector</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Customer complaint / 8D lesson learned</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>Observed source component for LL-PICTORIS-J73. CPN is the cross-product key; RefDes is board-specific.</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>MAP-TUFNELL-HI-U23-OLD</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>15-102981-01</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>TUFNELL PARK</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>73-20247-06</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>U23 material before released change</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>CRBU vs NGFWBU deviation analysis</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Structured from the documented U23 15-102981-01 to 15-102981-02 transition.</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MAP-TUFNELL-HI-U23-NEW</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>15-102981-02</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>TUFNELL PARK</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>73-20247-06</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>U23 material after released change</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>CRBU vs NGFWBU deviation analysis</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Structured from the documented U23 15-102981-01 to 15-102981-02 transition.</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MAP-TUFNELL-LO-U23-OLD</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>15-102981-01</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>TUFNELL PARK</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>73-20249-06</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>U23 material before released change</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>CRBU vs NGFWBU deviation analysis</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Structured from the documented U23 15-102981-01 to 15-102981-02 transition.</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>MAP-TUFNELL-LO-U23-NEW</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>15-102981-02</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>TUFNELL PARK</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>73-20249-06</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>U23</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>U23 material after released change</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>CRBU vs NGFWBU deviation analysis</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Structured from the documented U23 15-102981-01 to 15-102981-02 transition.</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3197,8 +3667,68 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Component CPN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Use the internal component/customer part number tied to the Yokoten finding or critical characteristic. This is the preferred cross-product search and inheritance key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>RefDes rule</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>RefDes is board-specific. J73 on one board is not assumed to be the same component as J73 on another board unless Component CPN or the Component Cross Reference confirms it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Component Cross Reference</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>One row per Component CPN + Board Part Number + RefDes mapping. Use this sheet to connect one component to every known product/board where it is used. Rev may be blank when the mapping applies to all revisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Component-level Yokoten</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>A finding with Component CPN may be inherited by another product only when Component Cross Reference maps that same CPN to the other board. Keep observed source findings distinct from inherited component exposure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Search contract</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SMTinel Yokoten search may use Product, Board Part Number, Revision, Component CPN, RefDes, MPN, Finding ID or failure/finding text. CPN search should return mapped products and their Common DB line/WO history.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/SMTinel_Yokoten_Knowledge_DB.xlsx
+++ b/SMTinel_Yokoten_Knowledge_DB.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qualification" sheetId="1" r:id="R4eba337f11104ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="R2ccc4eefeed34ca4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" r:id="R95226a3ee6d24096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical Characteristics" sheetId="4" r:id="R8fa33b122be74ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Cross Reference" sheetId="5" r:id="R1d43aa05486844bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="6" r:id="Rdea37634b50b423a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qualification" sheetId="1" r:id="R18b87577d26541c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" r:id="R79eb4ca709c841e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" r:id="Rd93f6e5d1e3648ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical Characteristics" sheetId="4" r:id="R246396dc5bf543a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Cross Reference" sheetId="5" r:id="Rf795cfccd7c54442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="6" r:id="Reea6defb9b0c4bcd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -84,7 +84,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -108,6 +108,9 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -234,7 +237,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Knowledge3" displayName="Knowledge3" ref="A1:M69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Knowledge3" displayName="Knowledge3" ref="A1:M69" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Action ID"/>
     <x:tableColumn id="2" name="Finding ID"/>
@@ -250,7 +253,7 @@
     <x:tableColumn id="12" name="Closure Note"/>
     <x:tableColumn id="13" name="Active"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -714,7 +717,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d7e89cdc79149dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f9837b51b084f65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2182,7 +2185,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13518fc2d9614015"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe909ea3f9ce4220"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2204,1935 +2207,1325 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Action ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finding ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Product</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Part Number</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rev</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Line</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Owner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Action</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Due Date</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Status</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Evidence Link</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Closure Note</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Active</x:t>
-        </x:is>
+      <x:c r="A1" s="1" t="str">
+        <x:v>Action ID</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>Finding ID</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>Part Number</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>Rev</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>Line</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="str">
+        <x:v>Due Date</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="str">
+        <x:v>Evidence Link</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="str">
+        <x:v>Closure Note</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="str">
+        <x:v>Active</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-J73-PNP</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-J73</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103603-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">B0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="2" t="n"/>
-      <x:c r="G2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Josué Rangel</x:t>
-        </x:is>
+      <x:c r="A2" s="2" t="str">
+        <x:v>ACT-PICTORIS-J73-PNP</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>LL-PICTORIS-J73</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="str">
+        <x:v>73-103603-05</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="str">
+        <x:v>B0</x:v>
+      </x:c>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2" t="str">
+        <x:v>Josué Rangel</x:v>
       </x:c>
       <x:c r="H2" s="2" t="str">
         <x:v>Corregir la orientación de J73 en los programas P&amp;P de L13 y L17 según el plano aprobado.</x:v>
       </x:c>
-      <x:c r="I2" s="4" t="n"/>
-      <x:c r="J2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Closed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" s="2" t="n"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="2" t="str">
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="K2" s="2"/>
       <x:c r="L2" s="2" t="str">
         <x:v>Cerrado según revisión 8D: se registró la corrección de orientación en P&amp;P.</x:v>
       </x:c>
-      <x:c r="M2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="M2" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="28" customHeight="1">
-      <x:c r="A3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-J73-AOI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-J73</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103603-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">B0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="2" t="n"/>
-      <x:c r="G3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Alberto Cruz</x:t>
-        </x:is>
+      <x:c r="A3" s="2" t="str">
+        <x:v>ACT-PICTORIS-J73-AOI</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>LL-PICTORIS-J73</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="str">
+        <x:v>73-103603-05</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="str">
+        <x:v>B0</x:v>
+      </x:c>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2" t="str">
+        <x:v>Alberto Cruz</x:v>
       </x:c>
       <x:c r="H3" s="2" t="str">
         <x:v>Ajustar AOI y probar una pieza correcta y otra con J73 girado 180° antes de liberar.</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="n"/>
-      <x:c r="J3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Closed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" s="2" t="n"/>
+      <x:c r="I3" s="4"/>
+      <x:c r="J3" s="2" t="str">
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="K3" s="2"/>
       <x:c r="L3" s="2" t="str">
         <x:v>Cerrado según revisión 8D: se probaron piezas con orientación correcta e invertida.</x:v>
       </x:c>
-      <x:c r="M3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="M3" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-J73-REQUAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-J73</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103603-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="2" t="n"/>
-      <x:c r="F4" s="2" t="n"/>
-      <x:c r="G4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Carlos Martínez</x:t>
-        </x:is>
+      <x:c r="A4" s="2" t="str">
+        <x:v>ACT-PICTORIS-J73-REQUAL</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>LL-PICTORIS-J73</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="str">
+        <x:v>73-103603-05</x:v>
+      </x:c>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2" t="str">
+        <x:v>Carlos Martínez</x:v>
       </x:c>
       <x:c r="H4" s="2" t="str">
         <x:v>Al calificar o recalificar una línea, revisar orientación P&amp;P, prueba AOI correcto/invertido y primera pieza antes de liberar.</x:v>
       </x:c>
-      <x:c r="I4" s="4" t="n"/>
-      <x:c r="J4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" s="2" t="n"/>
-      <x:c r="L4" s="2" t="str"/>
-      <x:c r="M4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-J73-TEST-COVERAGE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-J73</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103603-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="2" t="n"/>
-      <x:c r="F5" s="2" t="n"/>
-      <x:c r="G5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">David Pacheco</x:t>
-        </x:is>
+      <x:c r="A5" s="2" t="str">
+        <x:v>ACT-PICTORIS-J73-TEST-COVERAGE</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>LL-PICTORIS-J73</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="str">
+        <x:v>73-103603-05</x:v>
+      </x:c>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2" t="str">
+        <x:v>David Pacheco</x:v>
       </x:c>
       <x:c r="H5" s="2" t="str">
         <x:v>Revisar si las pruebas detectan J73 al revés. No contar la prueba funcional como control de orientación sin evidencia.</x:v>
       </x:c>
-      <x:c r="I5" s="4" t="n"/>
-      <x:c r="J5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K5" s="2" t="n"/>
-      <x:c r="L5" s="2" t="str"/>
-      <x:c r="M5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I5" s="4"/>
+      <x:c r="J5" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K5" s="2"/>
+      <x:c r="L5" s="2"/>
+      <x:c r="M5" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
-      <x:c r="A6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-WO-PN-REV-BLOCK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-WO-IDENTITY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103603-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="2" t="n"/>
-      <x:c r="F6" s="2" t="n"/>
-      <x:c r="G6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planeación / PM</x:t>
-        </x:is>
+      <x:c r="A6" s="2" t="str">
+        <x:v>ACT-PICTORIS-WO-PN-REV-BLOCK</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>LL-PICTORIS-WO-IDENTITY</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="str">
+        <x:v>73-103603-05</x:v>
+      </x:c>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2" t="str">
+        <x:v>Planeación / PM</x:v>
       </x:c>
       <x:c r="H6" s="2" t="str">
         <x:v>Agregar un bloqueo para impedir crear o liberar órdenes con número de parte o revisión incorrectos.</x:v>
       </x:c>
-      <x:c r="I6" s="4" t="n"/>
-      <x:c r="J6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K6" s="2" t="n"/>
-      <x:c r="L6" s="2" t="str"/>
-      <x:c r="M6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K6" s="2"/>
+      <x:c r="L6" s="2"/>
+      <x:c r="M6" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-WO-FIRST-PIECE-ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-WO-IDENTITY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103603-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="2" t="n"/>
-      <x:c r="F7" s="2" t="n"/>
-      <x:c r="G7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planeación / PM</x:t>
-        </x:is>
+      <x:c r="A7" s="2" t="str">
+        <x:v>ACT-PICTORIS-WO-FIRST-PIECE-ID</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>LL-PICTORIS-WO-IDENTITY</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="str">
+        <x:v>73-103603-05</x:v>
+      </x:c>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2" t="str">
+        <x:v>Planeación / PM</x:v>
       </x:c>
       <x:c r="H7" s="2" t="str">
         <x:v>Antes de producir, confirmar modelo, número de parte y revisión en la primera pieza. Corregir cualquier diferencia en la orden.</x:v>
       </x:c>
-      <x:c r="I7" s="4" t="n"/>
-      <x:c r="J7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K7" s="2" t="n"/>
-      <x:c r="L7" s="2" t="str"/>
-      <x:c r="M7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K7" s="2"/>
+      <x:c r="L7" s="2"/>
+      <x:c r="M7" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-BAYFRONT-BOM-LOADLIST-CHECK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-BAYFRONT-BOM-LOADLIST</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BAYFRONT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103826-05</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="2" t="n"/>
-      <x:c r="F8" s="2" t="n"/>
-      <x:c r="G8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Programación / Calidad</x:t>
-        </x:is>
+      <x:c r="A8" s="2" t="str">
+        <x:v>ACT-BAYFRONT-BOM-LOADLIST-CHECK</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>LL-BAYFRONT-BOM-LOADLIST</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>BAYFRONT</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="str">
+        <x:v>73-103826-05</x:v>
+      </x:c>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2" t="str">
+        <x:v>Programación / Calidad</x:v>
       </x:c>
       <x:c r="H8" s="2" t="str">
         <x:v>Comparar automáticamente número de parte, posición, cantidad y revisión entre BOM y lista de carga antes de aprobar.</x:v>
       </x:c>
-      <x:c r="I8" s="4" t="n"/>
-      <x:c r="J8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K8" s="2" t="n"/>
-      <x:c r="L8" s="2" t="str"/>
-      <x:c r="M8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K8" s="2"/>
+      <x:c r="L8" s="2"/>
+      <x:c r="M8" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-ARATA-U58-CONFIG-GATE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-ARATA-ODM-CONFIG</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ARATA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">74-133408-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">B0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="2" t="n"/>
-      <x:c r="G9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Planeación / Producto / SMT / ICT</x:t>
-        </x:is>
+      <x:c r="A9" s="2" t="str">
+        <x:v>ACT-ARATA-U58-CONFIG-GATE</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>LL-ARATA-ODM-CONFIG</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="str">
+        <x:v>ARATA</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="str">
+        <x:v>74-133408-02</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="str">
+        <x:v>B0</x:v>
+      </x:c>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2" t="str">
+        <x:v>Planeación / Producto / SMT / ICT</x:v>
       </x:c>
       <x:c r="H9" s="2" t="str">
         <x:v>Registrar U58, revisión y documento de cambio en la orden. Completar la revisión conjunta antes de liberar.</x:v>
       </x:c>
-      <x:c r="I9" s="4" t="n"/>
-      <x:c r="J9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K9" s="2" t="n"/>
-      <x:c r="L9" s="2" t="str"/>
-      <x:c r="M9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K9" s="2"/>
+      <x:c r="L9" s="2"/>
+      <x:c r="M9" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-ARATA-ICT-CHANGE-VALIDATION</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-ARATA-ODM-CONFIG</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ARATA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">74-133408-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">B0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="2" t="n"/>
-      <x:c r="G10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ICT / Planeación / SMT</x:t>
-        </x:is>
+      <x:c r="A10" s="2" t="str">
+        <x:v>ACT-ARATA-ICT-CHANGE-VALIDATION</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="str">
+        <x:v>LL-ARATA-ODM-CONFIG</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="str">
+        <x:v>ARATA</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="str">
+        <x:v>74-133408-02</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="str">
+        <x:v>B0</x:v>
+      </x:c>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2" t="str">
+        <x:v>ICT / Planeación / SMT</x:v>
       </x:c>
       <x:c r="H10" s="2" t="str">
         <x:v>Antes de liberar un cambio, confirmar que ICT tenga las pruebas correctas para la configuración física, incluida U602 cuando aplique.</x:v>
       </x:c>
-      <x:c r="I10" s="4" t="n"/>
-      <x:c r="J10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K10" s="2" t="n"/>
-      <x:c r="L10" s="2" t="str"/>
-      <x:c r="M10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K10" s="2"/>
+      <x:c r="L10" s="2"/>
+      <x:c r="M10" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-ARATA-REFDES-CLOSEOUT</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-ARATA-ODM-CONFIG</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ARATA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">74-133408-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">B0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="2" t="n"/>
-      <x:c r="G11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SMT / ICT</x:t>
-        </x:is>
+      <x:c r="A11" s="2" t="str">
+        <x:v>ACT-ARATA-REFDES-CLOSEOUT</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>LL-ARATA-ODM-CONFIG</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="str">
+        <x:v>ARATA</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="str">
+        <x:v>74-133408-02</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="str">
+        <x:v>B0</x:v>
+      </x:c>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2" t="str">
+        <x:v>SMT / ICT</x:v>
       </x:c>
       <x:c r="H11" s="2" t="str">
         <x:v>Antes de liberar la orden, revisar cada posición afectada y confirmar el cambio físico y las pruebas correspondientes.</x:v>
       </x:c>
-      <x:c r="I11" s="4" t="n"/>
-      <x:c r="J11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K11" s="2" t="n"/>
-      <x:c r="L11" s="2" t="str"/>
-      <x:c r="M11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K11" s="2"/>
+      <x:c r="L11" s="2"/>
+      <x:c r="M11" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TAYLOR-PNP-DEBUG</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TAYLOR-LARGE-BODY-CLEARANCE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TAYLOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="2" t="n"/>
-      <x:c r="E12" s="2" t="n"/>
-      <x:c r="F12" s="2" t="n"/>
-      <x:c r="G12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Josué Rangel</x:t>
-        </x:is>
+      <x:c r="A12" s="2" t="str">
+        <x:v>ACT-TAYLOR-PNP-DEBUG</x:v>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>LL-TAYLOR-LARGE-BODY-CLEARANCE</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="str">
+        <x:v>TAYLOR</x:v>
+      </x:c>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2" t="str">
+        <x:v>Josué Rangel</x:v>
       </x:c>
       <x:c r="H12" s="2" t="str">
         <x:v>Revisar las zonas críticas en el modo de ajuste P&amp;P. Confirmar pieza, centrado, posición, ángulo y separación con muestras buenas y malas.</x:v>
       </x:c>
-      <x:c r="I12" s="4" t="n"/>
-      <x:c r="J12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K12" s="2" t="n"/>
-      <x:c r="L12" s="2" t="str"/>
-      <x:c r="M12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K12" s="2"/>
+      <x:c r="L12" s="2"/>
+      <x:c r="M12" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TAYLOR-AOI-CLEARANCE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TAYLOR-LARGE-BODY-CLEARANCE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TAYLOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="2" t="n"/>
-      <x:c r="E13" s="2" t="n"/>
-      <x:c r="F13" s="2" t="n"/>
-      <x:c r="G13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">José Cruz</x:t>
-        </x:is>
+      <x:c r="A13" s="2" t="str">
+        <x:v>ACT-TAYLOR-AOI-CLEARANCE</x:v>
+      </x:c>
+      <x:c r="B13" s="2" t="str">
+        <x:v>LL-TAYLOR-LARGE-BODY-CLEARANCE</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="str">
+        <x:v>TAYLOR</x:v>
+      </x:c>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2" t="str">
+        <x:v>José Cruz</x:v>
       </x:c>
       <x:c r="H13" s="2" t="str">
         <x:v>Ajustar AOI para revisar las posiciones críticas con muestras buenas y malas. Si no puede detectarlo, documentar otro método de inspección.</x:v>
       </x:c>
-      <x:c r="I13" s="4" t="n"/>
-      <x:c r="J13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K13" s="2" t="n"/>
-      <x:c r="L13" s="2" t="str"/>
-      <x:c r="M13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K13" s="2"/>
+      <x:c r="L13" s="2"/>
+      <x:c r="M13" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TAYLOR-AVL-BODY-ENVELOPE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TAYLOR-LARGE-BODY-CLEARANCE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TAYLOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="2" t="n"/>
-      <x:c r="E14" s="2" t="n"/>
-      <x:c r="F14" s="2" t="n"/>
-      <x:c r="G14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Carlos Martínez</x:t>
-        </x:is>
+      <x:c r="A14" s="2" t="str">
+        <x:v>ACT-TAYLOR-AVL-BODY-ENVELOPE</x:v>
+      </x:c>
+      <x:c r="B14" s="2" t="str">
+        <x:v>LL-TAYLOR-LARGE-BODY-CLEARANCE</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="str">
+        <x:v>TAYLOR</x:v>
+      </x:c>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2" t="str">
+        <x:v>Carlos Martínez</x:v>
       </x:c>
       <x:c r="H14" s="2" t="str">
         <x:v>Limitar las piezas grandes a tamaños aprobados para mantener la separación. Volver a revisar si cambia proveedor o modelo.</x:v>
       </x:c>
-      <x:c r="I14" s="4" t="n"/>
-      <x:c r="J14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K14" s="2" t="n"/>
-      <x:c r="L14" s="2" t="str"/>
-      <x:c r="M14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K14" s="2"/>
+      <x:c r="L14" s="2"/>
+      <x:c r="M14" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TAYLOR-XRAY-2000</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TAYLOR-LARGE-BODY-CLEARANCE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TAYLOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="2" t="n"/>
-      <x:c r="E15" s="2" t="n"/>
-      <x:c r="F15" s="2" t="n"/>
-      <x:c r="G15" s="2" t="n"/>
+      <x:c r="A15" s="2" t="str">
+        <x:v>ACT-TAYLOR-XRAY-2000</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="str">
+        <x:v>LL-TAYLOR-LARGE-BODY-CLEARANCE</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="str">
+        <x:v>TAYLOR</x:v>
+      </x:c>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
       <x:c r="H15" s="2" t="str">
         <x:v>Inspeccionar con rayos X las primeras 2,000 piezas de validación y vigilar las zonas críticas.</x:v>
       </x:c>
-      <x:c r="I15" s="4" t="n"/>
-      <x:c r="J15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monitoring</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="2" t="n"/>
-      <x:c r="L15" s="2" t="str"/>
-      <x:c r="M15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="2" t="str">
+        <x:v>Monitoring</x:v>
+      </x:c>
+      <x:c r="K15" s="2"/>
+      <x:c r="L15" s="2"/>
+      <x:c r="M15" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-NIXIE-PNP-NOZZLE-STANDARD</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-NIXIE-MIC-SEATING</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NIXIE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="2" t="n"/>
-      <x:c r="E16" s="2" t="n"/>
-      <x:c r="F16" s="2" t="n"/>
-      <x:c r="G16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SMT-P&amp;P</x:t>
-        </x:is>
+      <x:c r="A16" s="2" t="str">
+        <x:v>ACT-NIXIE-PNP-NOZZLE-STANDARD</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="str">
+        <x:v>LL-NIXIE-MIC-SEATING</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="str">
+        <x:v>NIXIE</x:v>
+      </x:c>
+      <x:c r="D16" s="2"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+      <x:c r="G16" s="2" t="str">
+        <x:v>SMT-P&amp;P</x:v>
       </x:c>
       <x:c r="H16" s="2" t="str">
         <x:v>Definir la boquilla y los ajustes P&amp;P del micrófono según la hoja del proveedor. Controlar la presión al colocarlo.</x:v>
       </x:c>
-      <x:c r="I16" s="4" t="n"/>
-      <x:c r="J16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="2" t="str">
+        <x:v>Open</x:v>
       </x:c>
       <x:c r="K16" s="2" t="str">
         <x:v>https://chatgpt.com/c/6ab960a3-208c-83e8-8009-8c18a39dd451</x:v>
       </x:c>
-      <x:c r="L16" s="2" t="str"/>
-      <x:c r="M16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="L16" s="2"/>
+      <x:c r="M16" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-NIXIE-GETTOP-WK10-SAFELAUNCH</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-NIXIE-MIC-SEATING</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NIXIE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="2" t="n"/>
-      <x:c r="E17" s="2" t="n"/>
-      <x:c r="F17" s="2" t="n"/>
-      <x:c r="G17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quality / Carlos Martínez</x:t>
-        </x:is>
+      <x:c r="A17" s="2" t="str">
+        <x:v>ACT-NIXIE-GETTOP-WK10-SAFELAUNCH</x:v>
+      </x:c>
+      <x:c r="B17" s="2" t="str">
+        <x:v>LL-NIXIE-MIC-SEATING</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="str">
+        <x:v>NIXIE</x:v>
+      </x:c>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2" t="str">
+        <x:v>Quality / Carlos Martínez</x:v>
       </x:c>
       <x:c r="H17" s="2" t="str">
         <x:v>Durante la validación WK10 / WO1290100, usar solo GETTOP MD-HRA261-H10-2 y mantener MERRY bloqueado. Revisar después de colocar y soldar.</x:v>
       </x:c>
-      <x:c r="I17" s="4" t="n"/>
-      <x:c r="J17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monitoring</x:t>
-        </x:is>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="2" t="str">
+        <x:v>Monitoring</x:v>
       </x:c>
       <x:c r="K17" s="2" t="str">
         <x:v>https://chatgpt.com/c/6ab960a3-208c-83e8-8009-8c18a39dd451</x:v>
       </x:c>
-      <x:c r="L17" s="2" t="str"/>
-      <x:c r="M17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="L17" s="2"/>
+      <x:c r="M17" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TUFNELL-HI-BLOCK-TOSHIBA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TUFNELL-DEVIATION-SCOPE-HI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TUFNELL PARK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-20247-06</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="2" t="n"/>
-      <x:c r="F18" s="2" t="n"/>
-      <x:c r="G18" s="2" t="n"/>
+      <x:c r="A18" s="2" t="str">
+        <x:v>ACT-TUFNELL-HI-BLOCK-TOSHIBA</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="str">
+        <x:v>LL-TUFNELL-DEVIATION-SCOPE-HI</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="str">
+        <x:v>TUFNELL PARK</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="str">
+        <x:v>73-20247-06</x:v>
+      </x:c>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+      <x:c r="G18" s="2"/>
       <x:c r="H18" s="2" t="str">
         <x:v>Bloquear material Toshiba para NGFWBU hasta corregir el alcance de la desviación. La aprobación de CRBU no autoriza su uso en NGFWBU.</x:v>
       </x:c>
-      <x:c r="I18" s="4" t="n"/>
-      <x:c r="J18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monitoring</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="2" t="n"/>
-      <x:c r="L18" s="2" t="str"/>
-      <x:c r="M18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="2" t="str">
+        <x:v>Monitoring</x:v>
+      </x:c>
+      <x:c r="K18" s="2"/>
+      <x:c r="L18" s="2"/>
+      <x:c r="M18" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TUFNELL-HI-DEVIATION-SCOPE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TUFNELL-DEVIATION-SCOPE-HI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TUFNELL PARK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-20247-06</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="2" t="n"/>
-      <x:c r="F19" s="2" t="n"/>
-      <x:c r="G19" s="2" t="n"/>
+      <x:c r="A19" s="2" t="str">
+        <x:v>ACT-TUFNELL-HI-DEVIATION-SCOPE</x:v>
+      </x:c>
+      <x:c r="B19" s="2" t="str">
+        <x:v>LL-TUFNELL-DEVIATION-SCOPE-HI</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="str">
+        <x:v>TUFNELL PARK</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="str">
+        <x:v>73-20247-06</x:v>
+      </x:c>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
       <x:c r="H19" s="2" t="str">
         <x:v>Antes de aplicar una desviación, confirmar unidad de negocio, producto y orden. Si no coinciden, mantener el bloqueo en SAP.</x:v>
       </x:c>
-      <x:c r="I19" s="4" t="n"/>
-      <x:c r="J19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="2" t="n"/>
-      <x:c r="L19" s="2" t="str"/>
-      <x:c r="M19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K19" s="2"/>
+      <x:c r="L19" s="2"/>
+      <x:c r="M19" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TUFNELL-LO-BLOCK-TOSHIBA</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TUFNELL-DEVIATION-SCOPE-LO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TUFNELL PARK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-20249-06</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="2" t="n"/>
-      <x:c r="F20" s="2" t="n"/>
-      <x:c r="G20" s="2" t="n"/>
+      <x:c r="A20" s="2" t="str">
+        <x:v>ACT-TUFNELL-LO-BLOCK-TOSHIBA</x:v>
+      </x:c>
+      <x:c r="B20" s="2" t="str">
+        <x:v>LL-TUFNELL-DEVIATION-SCOPE-LO</x:v>
+      </x:c>
+      <x:c r="C20" s="2" t="str">
+        <x:v>TUFNELL PARK</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="str">
+        <x:v>73-20249-06</x:v>
+      </x:c>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
       <x:c r="H20" s="2" t="str">
         <x:v>Bloquear material Toshiba para NGFWBU hasta corregir el alcance de la desviación. La aprobación de CRBU no autoriza su uso en NGFWBU.</x:v>
       </x:c>
-      <x:c r="I20" s="4" t="n"/>
-      <x:c r="J20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monitoring</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K20" s="2" t="n"/>
-      <x:c r="L20" s="2" t="str"/>
-      <x:c r="M20" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="2" t="str">
+        <x:v>Monitoring</x:v>
+      </x:c>
+      <x:c r="K20" s="2"/>
+      <x:c r="L20" s="2"/>
+      <x:c r="M20" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-TUFNELL-LO-DEVIATION-SCOPE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-TUFNELL-DEVIATION-SCOPE-LO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TUFNELL PARK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-20249-06</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="2" t="n"/>
-      <x:c r="F21" s="2" t="n"/>
-      <x:c r="G21" s="2" t="n"/>
+      <x:c r="A21" s="2" t="str">
+        <x:v>ACT-TUFNELL-LO-DEVIATION-SCOPE</x:v>
+      </x:c>
+      <x:c r="B21" s="2" t="str">
+        <x:v>LL-TUFNELL-DEVIATION-SCOPE-LO</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="str">
+        <x:v>TUFNELL PARK</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="str">
+        <x:v>73-20249-06</x:v>
+      </x:c>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
       <x:c r="H21" s="2" t="str">
         <x:v>Antes de aplicar una desviación, confirmar unidad de negocio, producto y orden. Si no coinciden, mantener el bloqueo en SAP.</x:v>
       </x:c>
-      <x:c r="I21" s="4" t="n"/>
-      <x:c r="J21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K21" s="2" t="n"/>
-      <x:c r="L21" s="2" t="str"/>
-      <x:c r="M21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="I21" s="4"/>
+      <x:c r="J21" s="2" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K21" s="2"/>
+      <x:c r="L21" s="2"/>
+      <x:c r="M21" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-CHARON-CR95-SOP-VISUAL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-CHARON-CR95-POLARITY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CHARON</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" s="2" t="n"/>
-      <x:c r="E22" s="2" t="n"/>
-      <x:c r="F22" s="2" t="n"/>
-      <x:c r="G22" s="2" t="n"/>
+      <x:c r="A22" s="2" t="str">
+        <x:v>ACT-CHARON-CR95-SOP-VISUAL</x:v>
+      </x:c>
+      <x:c r="B22" s="2" t="str">
+        <x:v>LL-CHARON-CR95-POLARITY</x:v>
+      </x:c>
+      <x:c r="C22" s="2" t="str">
+        <x:v>CHARON</x:v>
+      </x:c>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
       <x:c r="H22" s="2" t="str">
         <x:v>Agregar una ayuda visual al procedimiento SMT para CR95. Confirmar en producción que la marca verde quede opuesta a la marca de polaridad de la tablilla.</x:v>
       </x:c>
-      <x:c r="I22" s="4" t="n"/>
-      <x:c r="J22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Closed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K22" s="2" t="n"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="2" t="str">
+        <x:v>Closed</x:v>
+      </x:c>
+      <x:c r="K22" s="2"/>
       <x:c r="L22" s="2" t="str">
         <x:v>La revisión posterior indicó que la ayuda visual se cerró durante NPI. La marca verde indica ánodo y va opuesta al silkscreen.</x:v>
       </x:c>
-      <x:c r="M22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="M22" s="2" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="39.5" customHeight="1">
-      <x:c r="A23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-BOTON-FLUX-PROTEGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" s="8" t="n"/>
-      <x:c r="E23" s="8" t="n"/>
-      <x:c r="F23" s="8" t="n"/>
-      <x:c r="G23" s="8" t="n"/>
-      <x:c r="H23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I23" s="8" t="n"/>
-      <x:c r="J23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K23" s="8" t="n"/>
-      <x:c r="L23" s="8" t="n"/>
-      <x:c r="M23" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A23" s="8" t="str">
+        <x:v>ACT-PICTORIS-BOTON-FLUX-PROTEGER</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>LL-PICTORIS-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D23" s="8"/>
+      <x:c r="E23" s="8"/>
+      <x:c r="F23" s="8"/>
+      <x:c r="G23" s="8"/>
+      <x:c r="H23" s="8" t="str">
+        <x:v>No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:v>
+      </x:c>
+      <x:c r="I23" s="8"/>
+      <x:c r="J23" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K23" s="8"/>
+      <x:c r="L23" s="8"/>
+      <x:c r="M23" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="66" customHeight="1">
-      <x:c r="A24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-BOTON-FLUX-REEMPLAZAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" s="8" t="n"/>
-      <x:c r="E24" s="8" t="n"/>
-      <x:c r="F24" s="8" t="n"/>
-      <x:c r="G24" s="8" t="n"/>
-      <x:c r="H24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" s="8" t="n"/>
-      <x:c r="J24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K24" s="8" t="n"/>
-      <x:c r="L24" s="8" t="n"/>
-      <x:c r="M24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A24" s="8" t="str">
+        <x:v>ACT-PICTORIS-BOTON-FLUX-REEMPLAZAR</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="str">
+        <x:v>LL-PICTORIS-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D24" s="8"/>
+      <x:c r="E24" s="8"/>
+      <x:c r="F24" s="8"/>
+      <x:c r="G24" s="8"/>
+      <x:c r="H24" s="8" t="str">
+        <x:v>Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:v>
+      </x:c>
+      <x:c r="I24" s="8"/>
+      <x:c r="J24" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K24" s="8"/>
+      <x:c r="L24" s="8"/>
+      <x:c r="M24" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="52.75" customHeight="1">
-      <x:c r="A25" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-PICTORIS-BOTON-FLUX-VERIFICAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B25" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-PICTORIS-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PICTORIS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" s="8" t="n"/>
-      <x:c r="E25" s="8" t="n"/>
-      <x:c r="F25" s="8" t="n"/>
-      <x:c r="G25" s="8" t="n"/>
-      <x:c r="H25" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" s="8" t="n"/>
-      <x:c r="J25" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K25" s="8" t="n"/>
-      <x:c r="L25" s="8" t="n"/>
-      <x:c r="M25" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A25" s="8" t="str">
+        <x:v>ACT-PICTORIS-BOTON-FLUX-VERIFICAR</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="str">
+        <x:v>LL-PICTORIS-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="str">
+        <x:v>PICTORIS</x:v>
+      </x:c>
+      <x:c r="D25" s="8"/>
+      <x:c r="E25" s="8"/>
+      <x:c r="F25" s="8"/>
+      <x:c r="G25" s="8"/>
+      <x:c r="H25" s="8" t="str">
+        <x:v>Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:v>
+      </x:c>
+      <x:c r="I25" s="8"/>
+      <x:c r="J25" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K25" s="8"/>
+      <x:c r="L25" s="8"/>
+      <x:c r="M25" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="39.5" customHeight="1">
-      <x:c r="A26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-MILLENIUM-BOTON-FLUX-PROTEGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-MILLENIUM-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MILLENIUM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D26" s="8" t="n"/>
-      <x:c r="E26" s="8" t="n"/>
-      <x:c r="F26" s="8" t="n"/>
-      <x:c r="G26" s="8" t="n"/>
-      <x:c r="H26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I26" s="8" t="n"/>
-      <x:c r="J26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K26" s="8" t="n"/>
-      <x:c r="L26" s="8" t="n"/>
-      <x:c r="M26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A26" s="8" t="str">
+        <x:v>ACT-MILLENIUM-BOTON-FLUX-PROTEGER</x:v>
+      </x:c>
+      <x:c r="B26" s="8" t="str">
+        <x:v>LL-MILLENIUM-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C26" s="8" t="str">
+        <x:v>MILLENIUM</x:v>
+      </x:c>
+      <x:c r="D26" s="8"/>
+      <x:c r="E26" s="8"/>
+      <x:c r="F26" s="8"/>
+      <x:c r="G26" s="8"/>
+      <x:c r="H26" s="8" t="str">
+        <x:v>No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:v>
+      </x:c>
+      <x:c r="I26" s="8"/>
+      <x:c r="J26" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K26" s="8"/>
+      <x:c r="L26" s="8"/>
+      <x:c r="M26" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="66" customHeight="1">
-      <x:c r="A27" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-MILLENIUM-BOTON-FLUX-REEMPLAZAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B27" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-MILLENIUM-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MILLENIUM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D27" s="8" t="n"/>
-      <x:c r="E27" s="8" t="n"/>
-      <x:c r="F27" s="8" t="n"/>
-      <x:c r="G27" s="8" t="n"/>
-      <x:c r="H27" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I27" s="8" t="n"/>
-      <x:c r="J27" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K27" s="8" t="n"/>
-      <x:c r="L27" s="8" t="n"/>
-      <x:c r="M27" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A27" s="8" t="str">
+        <x:v>ACT-MILLENIUM-BOTON-FLUX-REEMPLAZAR</x:v>
+      </x:c>
+      <x:c r="B27" s="8" t="str">
+        <x:v>LL-MILLENIUM-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C27" s="8" t="str">
+        <x:v>MILLENIUM</x:v>
+      </x:c>
+      <x:c r="D27" s="8"/>
+      <x:c r="E27" s="8"/>
+      <x:c r="F27" s="8"/>
+      <x:c r="G27" s="8"/>
+      <x:c r="H27" s="8" t="str">
+        <x:v>Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:v>
+      </x:c>
+      <x:c r="I27" s="8"/>
+      <x:c r="J27" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K27" s="8"/>
+      <x:c r="L27" s="8"/>
+      <x:c r="M27" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="52.75" customHeight="1">
-      <x:c r="A28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-MILLENIUM-BOTON-FLUX-VERIFICAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-MILLENIUM-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MILLENIUM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D28" s="8" t="n"/>
-      <x:c r="E28" s="8" t="n"/>
-      <x:c r="F28" s="8" t="n"/>
-      <x:c r="G28" s="8" t="n"/>
-      <x:c r="H28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" s="8" t="n"/>
-      <x:c r="J28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K28" s="8" t="n"/>
-      <x:c r="L28" s="8" t="n"/>
-      <x:c r="M28" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A28" s="8" t="str">
+        <x:v>ACT-MILLENIUM-BOTON-FLUX-VERIFICAR</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="str">
+        <x:v>LL-MILLENIUM-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C28" s="8" t="str">
+        <x:v>MILLENIUM</x:v>
+      </x:c>
+      <x:c r="D28" s="8"/>
+      <x:c r="E28" s="8"/>
+      <x:c r="F28" s="8"/>
+      <x:c r="G28" s="8"/>
+      <x:c r="H28" s="8" t="str">
+        <x:v>Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:v>
+      </x:c>
+      <x:c r="I28" s="8"/>
+      <x:c r="J28" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K28" s="8"/>
+      <x:c r="L28" s="8"/>
+      <x:c r="M28" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="39.5" customHeight="1">
-      <x:c r="A29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-OCTAVIO-BOTON-FLUX-PROTEGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-OCTAVIO-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OCTAVIO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" s="8" t="n"/>
-      <x:c r="E29" s="8" t="n"/>
-      <x:c r="F29" s="8" t="n"/>
-      <x:c r="G29" s="8" t="n"/>
-      <x:c r="H29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I29" s="8" t="n"/>
-      <x:c r="J29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K29" s="8" t="n"/>
-      <x:c r="L29" s="8" t="n"/>
-      <x:c r="M29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A29" s="8" t="str">
+        <x:v>ACT-OCTAVIO-BOTON-FLUX-PROTEGER</x:v>
+      </x:c>
+      <x:c r="B29" s="8" t="str">
+        <x:v>LL-OCTAVIO-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C29" s="8" t="str">
+        <x:v>OCTAVIO</x:v>
+      </x:c>
+      <x:c r="D29" s="8"/>
+      <x:c r="E29" s="8"/>
+      <x:c r="F29" s="8"/>
+      <x:c r="G29" s="8"/>
+      <x:c r="H29" s="8" t="str">
+        <x:v>No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:v>
+      </x:c>
+      <x:c r="I29" s="8"/>
+      <x:c r="J29" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K29" s="8"/>
+      <x:c r="L29" s="8"/>
+      <x:c r="M29" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="66" customHeight="1">
-      <x:c r="A30" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-OCTAVIO-BOTON-FLUX-REEMPLAZAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-OCTAVIO-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OCTAVIO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" s="8" t="n"/>
-      <x:c r="E30" s="8" t="n"/>
-      <x:c r="F30" s="8" t="n"/>
-      <x:c r="G30" s="8" t="n"/>
-      <x:c r="H30" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" s="8" t="n"/>
-      <x:c r="J30" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K30" s="8" t="n"/>
-      <x:c r="L30" s="8" t="n"/>
-      <x:c r="M30" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A30" s="8" t="str">
+        <x:v>ACT-OCTAVIO-BOTON-FLUX-REEMPLAZAR</x:v>
+      </x:c>
+      <x:c r="B30" s="8" t="str">
+        <x:v>LL-OCTAVIO-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C30" s="8" t="str">
+        <x:v>OCTAVIO</x:v>
+      </x:c>
+      <x:c r="D30" s="8"/>
+      <x:c r="E30" s="8"/>
+      <x:c r="F30" s="8"/>
+      <x:c r="G30" s="8"/>
+      <x:c r="H30" s="8" t="str">
+        <x:v>Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:v>
+      </x:c>
+      <x:c r="I30" s="8"/>
+      <x:c r="J30" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K30" s="8"/>
+      <x:c r="L30" s="8"/>
+      <x:c r="M30" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="52.75" customHeight="1">
-      <x:c r="A31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-OCTAVIO-BOTON-FLUX-VERIFICAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-OCTAVIO-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OCTAVIO</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" s="8" t="n"/>
-      <x:c r="E31" s="8" t="n"/>
-      <x:c r="F31" s="8" t="n"/>
-      <x:c r="G31" s="8" t="n"/>
-      <x:c r="H31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" s="8" t="n"/>
-      <x:c r="J31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K31" s="8" t="n"/>
-      <x:c r="L31" s="8" t="n"/>
-      <x:c r="M31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A31" s="8" t="str">
+        <x:v>ACT-OCTAVIO-BOTON-FLUX-VERIFICAR</x:v>
+      </x:c>
+      <x:c r="B31" s="8" t="str">
+        <x:v>LL-OCTAVIO-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C31" s="8" t="str">
+        <x:v>OCTAVIO</x:v>
+      </x:c>
+      <x:c r="D31" s="8"/>
+      <x:c r="E31" s="8"/>
+      <x:c r="F31" s="8"/>
+      <x:c r="G31" s="8"/>
+      <x:c r="H31" s="8" t="str">
+        <x:v>Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:v>
+      </x:c>
+      <x:c r="I31" s="8"/>
+      <x:c r="J31" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K31" s="8"/>
+      <x:c r="L31" s="8"/>
+      <x:c r="M31" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="39.5" customHeight="1">
-      <x:c r="A32" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-BROOKLYN-BOTON-FLUX-PROTEGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-BROOKLYN-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C32" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BROOKLYN</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" s="8" t="n"/>
-      <x:c r="E32" s="8" t="n"/>
-      <x:c r="F32" s="8" t="n"/>
-      <x:c r="G32" s="8" t="n"/>
-      <x:c r="H32" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" s="8" t="n"/>
-      <x:c r="J32" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K32" s="8" t="n"/>
-      <x:c r="L32" s="8" t="n"/>
-      <x:c r="M32" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A32" s="8" t="str">
+        <x:v>ACT-BROOKLYN-BOTON-FLUX-PROTEGER</x:v>
+      </x:c>
+      <x:c r="B32" s="8" t="str">
+        <x:v>LL-BROOKLYN-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C32" s="8" t="str">
+        <x:v>BROOKLYN</x:v>
+      </x:c>
+      <x:c r="D32" s="8"/>
+      <x:c r="E32" s="8"/>
+      <x:c r="F32" s="8"/>
+      <x:c r="G32" s="8"/>
+      <x:c r="H32" s="8" t="str">
+        <x:v>No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:v>
+      </x:c>
+      <x:c r="I32" s="8"/>
+      <x:c r="J32" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K32" s="8"/>
+      <x:c r="L32" s="8"/>
+      <x:c r="M32" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="66" customHeight="1">
-      <x:c r="A33" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-BROOKLYN-BOTON-FLUX-REEMPLAZAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B33" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-BROOKLYN-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BROOKLYN</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" s="8" t="n"/>
-      <x:c r="E33" s="8" t="n"/>
-      <x:c r="F33" s="8" t="n"/>
-      <x:c r="G33" s="8" t="n"/>
-      <x:c r="H33" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" s="8" t="n"/>
-      <x:c r="J33" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K33" s="8" t="n"/>
-      <x:c r="L33" s="8" t="n"/>
-      <x:c r="M33" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A33" s="8" t="str">
+        <x:v>ACT-BROOKLYN-BOTON-FLUX-REEMPLAZAR</x:v>
+      </x:c>
+      <x:c r="B33" s="8" t="str">
+        <x:v>LL-BROOKLYN-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C33" s="8" t="str">
+        <x:v>BROOKLYN</x:v>
+      </x:c>
+      <x:c r="D33" s="8"/>
+      <x:c r="E33" s="8"/>
+      <x:c r="F33" s="8"/>
+      <x:c r="G33" s="8"/>
+      <x:c r="H33" s="8" t="str">
+        <x:v>Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:v>
+      </x:c>
+      <x:c r="I33" s="8"/>
+      <x:c r="J33" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K33" s="8"/>
+      <x:c r="L33" s="8"/>
+      <x:c r="M33" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="52.75" customHeight="1">
-      <x:c r="A34" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-BROOKLYN-BOTON-FLUX-VERIFICAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B34" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-BROOKLYN-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C34" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BROOKLYN</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" s="8" t="n"/>
-      <x:c r="E34" s="8" t="n"/>
-      <x:c r="F34" s="8" t="n"/>
-      <x:c r="G34" s="8" t="n"/>
-      <x:c r="H34" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" s="8" t="n"/>
-      <x:c r="J34" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K34" s="8" t="n"/>
-      <x:c r="L34" s="8" t="n"/>
-      <x:c r="M34" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A34" s="8" t="str">
+        <x:v>ACT-BROOKLYN-BOTON-FLUX-VERIFICAR</x:v>
+      </x:c>
+      <x:c r="B34" s="8" t="str">
+        <x:v>LL-BROOKLYN-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C34" s="8" t="str">
+        <x:v>BROOKLYN</x:v>
+      </x:c>
+      <x:c r="D34" s="8"/>
+      <x:c r="E34" s="8"/>
+      <x:c r="F34" s="8"/>
+      <x:c r="G34" s="8"/>
+      <x:c r="H34" s="8" t="str">
+        <x:v>Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:v>
+      </x:c>
+      <x:c r="I34" s="8"/>
+      <x:c r="J34" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K34" s="8"/>
+      <x:c r="L34" s="8"/>
+      <x:c r="M34" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="39.5" customHeight="1">
-      <x:c r="A35" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-DAVINCI-BOTON-FLUX-PROTEGER</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B35" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-DAVINCI-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C35" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DAVINCI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" s="8" t="n"/>
-      <x:c r="E35" s="8" t="n"/>
-      <x:c r="F35" s="8" t="n"/>
-      <x:c r="G35" s="8" t="n"/>
-      <x:c r="H35" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" s="8" t="n"/>
-      <x:c r="J35" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K35" s="8" t="n"/>
-      <x:c r="L35" s="8" t="n"/>
-      <x:c r="M35" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A35" s="8" t="str">
+        <x:v>ACT-DAVINCI-BOTON-FLUX-PROTEGER</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="str">
+        <x:v>LL-DAVINCI-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C35" s="8" t="str">
+        <x:v>DAVINCI</x:v>
+      </x:c>
+      <x:c r="D35" s="8"/>
+      <x:c r="E35" s="8"/>
+      <x:c r="F35" s="8"/>
+      <x:c r="G35" s="8"/>
+      <x:c r="H35" s="8" t="str">
+        <x:v>No aplicar flux al botón, su cuerpo ni sus aberturas. Cubrir con Kapton toda el área de conectores y proteger el botón sin presionar el actuador. Mantener la protección durante el retrabajo.</x:v>
+      </x:c>
+      <x:c r="I35" s="8"/>
+      <x:c r="J35" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K35" s="8"/>
+      <x:c r="L35" s="8"/>
+      <x:c r="M35" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="66" customHeight="1">
-      <x:c r="A36" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-DAVINCI-BOTON-FLUX-REEMPLAZAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B36" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-DAVINCI-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C36" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DAVINCI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D36" s="8" t="n"/>
-      <x:c r="E36" s="8" t="n"/>
-      <x:c r="F36" s="8" t="n"/>
-      <x:c r="G36" s="8" t="n"/>
-      <x:c r="H36" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I36" s="8" t="n"/>
-      <x:c r="J36" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K36" s="8" t="n"/>
-      <x:c r="L36" s="8" t="n"/>
-      <x:c r="M36" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A36" s="8" t="str">
+        <x:v>ACT-DAVINCI-BOTON-FLUX-REEMPLAZAR</x:v>
+      </x:c>
+      <x:c r="B36" s="8" t="str">
+        <x:v>LL-DAVINCI-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C36" s="8" t="str">
+        <x:v>DAVINCI</x:v>
+      </x:c>
+      <x:c r="D36" s="8"/>
+      <x:c r="E36" s="8"/>
+      <x:c r="F36" s="8"/>
+      <x:c r="G36" s="8"/>
+      <x:c r="H36" s="8" t="str">
+        <x:v>Inspeccionar el botón al 100 % antes y después del retrabajo. Si está húmedo por flux, pegajoso o con residuos, rechazar la unidad y reemplazar el componente completo por el método aprobado. No esperar a que se pegue. La limpieza o el funcionamiento temporal no sustituyen el reemplazo.</x:v>
+      </x:c>
+      <x:c r="I36" s="8"/>
+      <x:c r="J36" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K36" s="8"/>
+      <x:c r="L36" s="8"/>
+      <x:c r="M36" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="52.75" customHeight="1">
-      <x:c r="A37" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-DAVINCI-BOTON-FLUX-VERIFICAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B37" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-DAVINCI-BOTON-FLUX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C37" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DAVINCI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D37" s="8" t="n"/>
-      <x:c r="E37" s="8" t="n"/>
-      <x:c r="F37" s="8" t="n"/>
-      <x:c r="G37" s="8" t="n"/>
-      <x:c r="H37" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I37" s="8" t="n"/>
-      <x:c r="J37" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K37" s="8" t="n"/>
-      <x:c r="L37" s="8" t="n"/>
-      <x:c r="M37" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A37" s="8" t="str">
+        <x:v>ACT-DAVINCI-BOTON-FLUX-VERIFICAR</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>LL-DAVINCI-BOTON-FLUX</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="str">
+        <x:v>DAVINCI</x:v>
+      </x:c>
+      <x:c r="D37" s="8"/>
+      <x:c r="E37" s="8"/>
+      <x:c r="F37" s="8"/>
+      <x:c r="G37" s="8"/>
+      <x:c r="H37" s="8" t="str">
+        <x:v>Después del reemplazo, comprobar limpieza, accionamiento y retorno del botón. Ejecutar la prueba funcional aplicable y registrar el reemplazo y resultado por número de serie antes de liberar la unidad.</x:v>
+      </x:c>
+      <x:c r="I37" s="8"/>
+      <x:c r="J37" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K37" s="8"/>
+      <x:c r="L37" s="8"/>
+      <x:c r="M37" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="72" customHeight="1">
-      <x:c r="A38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-CLIP-REWORK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="8" t="n"/>
-      <x:c r="G38" s="8" t="n"/>
-      <x:c r="H38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Retrabajar la población afectada instalando el clip P/N 700-136420-01 en J3-J8 mediante el procedimiento aprobado. Verificar presencia, fijación, limpieza de la superficie dorada de contacto y ejecutar 100 % X-Ray en J3-J8 antes de liberar cada unidad.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I38" s="8" t="n"/>
-      <x:c r="J38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K38" s="8" t="n"/>
-      <x:c r="L38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contención / Producto</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M38" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A38" s="8" t="str">
+        <x:v>ACT-HEIMDALL-CLIP-REWORK</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D38" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E38" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F38" s="8"/>
+      <x:c r="G38" s="8"/>
+      <x:c r="H38" s="8" t="str">
+        <x:v>Retrabajar la población afectada instalando el clip P/N 700-136420-01 en J3-J8 mediante el procedimiento aprobado. Verificar presencia, fijación, limpieza de la superficie dorada de contacto y ejecutar 100 % X-Ray en J3-J8 antes de liberar cada unidad.</x:v>
+      </x:c>
+      <x:c r="I38" s="8"/>
+      <x:c r="J38" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K38" s="8"/>
+      <x:c r="L38" s="8" t="str">
+        <x:v>Contención / Producto</x:v>
+      </x:c>
+      <x:c r="M38" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="72" customHeight="1">
-      <x:c r="A39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-CLIP-PROCESS-DEFINITION</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F39" s="8" t="n"/>
-      <x:c r="G39" s="8" t="n"/>
-      <x:c r="H39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Definir y documentar de manera explícita dónde se instala el clip 700-136420-01, qué proceso acepta su custodia y cuál es el método de ensamble. Actualizar los documentos aplicables de proceso (lista de carga/programa, stencil cuando aplique, WI/SOP y criterio de inspección) para la revisión 73-103459-02 A0.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I39" s="8" t="n"/>
-      <x:c r="J39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K39" s="8" t="n"/>
-      <x:c r="L39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implementación de proceso</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M39" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A39" s="8" t="str">
+        <x:v>ACT-HEIMDALL-CLIP-PROCESS-DEFINITION</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C39" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D39" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E39" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F39" s="8"/>
+      <x:c r="G39" s="8"/>
+      <x:c r="H39" s="8" t="str">
+        <x:v>Definir y documentar de manera explícita dónde se instala el clip 700-136420-01, qué proceso acepta su custodia y cuál es el método de ensamble. Actualizar los documentos aplicables de proceso (lista de carga/programa, stencil cuando aplique, WI/SOP y criterio de inspección) para la revisión 73-103459-02 A0.</x:v>
+      </x:c>
+      <x:c r="I39" s="8"/>
+      <x:c r="J39" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K39" s="8"/>
+      <x:c r="L39" s="8" t="str">
+        <x:v>Implementación de proceso</x:v>
+      </x:c>
+      <x:c r="M39" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="72" customHeight="1">
-      <x:c r="A40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-PCAMAP-CUSTODY-GATE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F40" s="8" t="n"/>
-      <x:c r="G40" s="8" t="n"/>
-      <x:c r="H40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implementar el PCAMAP Reference Custody Gate: todo P/N afectado por ECN que tenga RefDes o relación física con la PCBA debe tener destino de manufactura, owner, método de ensamble, documento de control y método de verificación antes de liberar. La falta de palabras SMT/PTH/press-fit en la descripción no permite cerrar el ítem como N/A.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I40" s="8" t="n"/>
-      <x:c r="J40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K40" s="8" t="n"/>
-      <x:c r="L40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sistema / Prevención</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M40" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A40" s="8" t="str">
+        <x:v>ACT-HEIMDALL-PCAMAP-CUSTODY-GATE</x:v>
+      </x:c>
+      <x:c r="B40" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C40" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E40" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F40" s="8"/>
+      <x:c r="G40" s="8"/>
+      <x:c r="H40" s="8" t="str">
+        <x:v>Implementar el PCAMAP Reference Custody Gate: todo P/N afectado por ECN que tenga RefDes o relación física con la PCBA debe tener destino de manufactura, owner, método de ensamble, documento de control y método de verificación antes de liberar. La falta de palabras SMT/PTH/press-fit en la descripción no permite cerrar el ítem como N/A.</x:v>
+      </x:c>
+      <x:c r="I40" s="8"/>
+      <x:c r="J40" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K40" s="8"/>
+      <x:c r="L40" s="8" t="str">
+        <x:v>Sistema / Prevención</x:v>
+      </x:c>
+      <x:c r="M40" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="72" customHeight="1">
-      <x:c r="A41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-ECN-CFT-REVIEW</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F41" s="8" t="n"/>
-      <x:c r="G41" s="8" t="n"/>
-      <x:c r="H41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Incorporar esta revisión como punto obligatorio en las juntas de ECN/ECO. El CFT debe revisar activamente el delta de BOM/PCAMAP/drawing, asignar custodia por referencia y completar el checklist antes de aprobar la implementación. Una referencia sin owner o método definido permanece UNRESOLVED / HOLD.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I41" s="8" t="n"/>
-      <x:c r="J41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K41" s="8" t="n"/>
-      <x:c r="L41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sistema / ECN</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M41" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A41" s="8" t="str">
+        <x:v>ACT-HEIMDALL-ECN-CFT-REVIEW</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C41" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E41" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F41" s="8"/>
+      <x:c r="G41" s="8"/>
+      <x:c r="H41" s="8" t="str">
+        <x:v>Incorporar esta revisión como punto obligatorio en las juntas de ECN/ECO. El CFT debe revisar activamente el delta de BOM/PCAMAP/drawing, asignar custodia por referencia y completar el checklist antes de aprobar la implementación. Una referencia sin owner o método definido permanece UNRESOLVED / HOLD.</x:v>
+      </x:c>
+      <x:c r="I41" s="8"/>
+      <x:c r="J41" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K41" s="8"/>
+      <x:c r="L41" s="8" t="str">
+        <x:v>Sistema / ECN</x:v>
+      </x:c>
+      <x:c r="M41" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="72" customHeight="1">
-      <x:c r="A42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-CISCO-HEADUP</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="8" t="n"/>
-      <x:c r="G42" s="8" t="n"/>
-      <x:c r="H42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cuando el CFT no pueda determinar de forma concluyente dónde va una referencia, quién la ensambla o cómo debe implementarse con la documentación disponible, escalar un Head-Up / Technical Clarification al grupo de Cisco antes de liberar la construcción. No cerrar por suposición, prefijo de RefDes o descripción del material.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I42" s="8" t="n"/>
-      <x:c r="J42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K42" s="8" t="n"/>
-      <x:c r="L42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Escalación</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M42" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A42" s="8" t="str">
+        <x:v>ACT-HEIMDALL-CISCO-HEADUP</x:v>
+      </x:c>
+      <x:c r="B42" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C42" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D42" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E42" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F42" s="8"/>
+      <x:c r="G42" s="8"/>
+      <x:c r="H42" s="8" t="str">
+        <x:v>Cuando el CFT no pueda determinar de forma concluyente dónde va una referencia, quién la ensambla o cómo debe implementarse con la documentación disponible, escalar un Head-Up / Technical Clarification al grupo de Cisco antes de liberar la construcción. No cerrar por suposición, prefijo de RefDes o descripción del material.</x:v>
+      </x:c>
+      <x:c r="I42" s="8"/>
+      <x:c r="J42" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K42" s="8"/>
+      <x:c r="L42" s="8" t="str">
+        <x:v>Escalación</x:v>
+      </x:c>
+      <x:c r="M42" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="72" customHeight="1">
-      <x:c r="A43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-VECTOR-EXPOSURE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F43" s="8" t="n"/>
-      <x:c r="G43" s="8" t="n"/>
-      <x:c r="H43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Agregar en VECTOR el control de custodia por referencia y el cálculo de exposición desde la fecha de efectividad del cambio hasta la fecha de asignación/corrección: WOs, seriales, líneas, días de exposición y población potencial de retrabajo.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I43" s="8" t="n"/>
-      <x:c r="J43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K43" s="8" t="n"/>
-      <x:c r="L43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sistema / VECTOR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A43" s="8" t="str">
+        <x:v>ACT-HEIMDALL-VECTOR-EXPOSURE</x:v>
+      </x:c>
+      <x:c r="B43" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C43" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D43" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E43" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F43" s="8"/>
+      <x:c r="G43" s="8"/>
+      <x:c r="H43" s="8" t="str">
+        <x:v>Agregar en VECTOR el control de custodia por referencia y el cálculo de exposición desde la fecha de efectividad del cambio hasta la fecha de asignación/corrección: WOs, seriales, líneas, días de exposición y población potencial de retrabajo.</x:v>
+      </x:c>
+      <x:c r="I43" s="8"/>
+      <x:c r="J43" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K43" s="8"/>
+      <x:c r="L43" s="8" t="str">
+        <x:v>Sistema / VECTOR</x:v>
+      </x:c>
+      <x:c r="M43" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="72" customHeight="1">
-      <x:c r="A44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ACT-HEIMDALL-CUSTODY-EFFECTIVENESS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LL-HEIMDALL-CLIP-CUSTODY</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEIMDALL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">73-103459-02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F44" s="8" t="n"/>
-      <x:c r="G44" s="8" t="n"/>
-      <x:c r="H44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Verificar efectividad durante los siguientes 10 ECN aplicables o 90 días: 100 % de referencias agregadas/cambiadas con proceso, owner, método, documento y evidencia de verificación definidos antes de release; cero referencias cerradas como N/A sin justificación documentada y cero liberaciones con estatus UNRESOLVED.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I44" s="8" t="n"/>
-      <x:c r="J44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Open</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K44" s="8" t="n"/>
-      <x:c r="L44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Efectividad</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M44" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
+      <x:c r="A44" s="8" t="str">
+        <x:v>ACT-HEIMDALL-CUSTODY-EFFECTIVENESS</x:v>
+      </x:c>
+      <x:c r="B44" s="8" t="str">
+        <x:v>LL-HEIMDALL-CLIP-CUSTODY</x:v>
+      </x:c>
+      <x:c r="C44" s="8" t="str">
+        <x:v>HEIMDALL</x:v>
+      </x:c>
+      <x:c r="D44" s="8" t="str">
+        <x:v>73-103459-02</x:v>
+      </x:c>
+      <x:c r="E44" s="8" t="str">
+        <x:v>A0</x:v>
+      </x:c>
+      <x:c r="F44" s="8"/>
+      <x:c r="G44" s="8"/>
+      <x:c r="H44" s="8" t="str">
+        <x:v>Verificar efectividad durante los siguientes 10 ECN aplicables o 90 días: 100 % de referencias agregadas/cambiadas con proceso, owner, método, documento y evidencia de verificación definidos antes de release; cero referencias cerradas como N/A sin justificación documentada y cero liberaciones con estatus UNRESOLVED.</x:v>
+      </x:c>
+      <x:c r="I44" s="8"/>
+      <x:c r="J44" s="8" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="K44" s="8"/>
+      <x:c r="L44" s="8" t="str">
+        <x:v>Efectividad</x:v>
+      </x:c>
+      <x:c r="M44" s="8" t="str">
+        <x:v>Y</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -4148,13 +3541,13 @@
       <x:c r="D45" s="8" t="str">
         <x:v>73-104532-01</x:v>
       </x:c>
-      <x:c r="E45" s="8" t="str"/>
-      <x:c r="F45" s="8" t="str"/>
-      <x:c r="G45" s="8" t="str"/>
+      <x:c r="E45" s="8"/>
+      <x:c r="F45" s="8"/>
+      <x:c r="G45" s="8"/>
       <x:c r="H45" s="8" t="str">
         <x:v>Obtener y publicar la referencia oficial de aceptación por CPN/programación, con foto del marcado permitido, fuente de autorización y revisión accesible a los tres turnos.</x:v>
       </x:c>
-      <x:c r="I45" s="8" t="str"/>
+      <x:c r="I45" s="8"/>
       <x:c r="J45" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4181,13 +3574,13 @@
       <x:c r="D46" s="8" t="str">
         <x:v>73-104532-01</x:v>
       </x:c>
-      <x:c r="E46" s="8" t="str"/>
-      <x:c r="F46" s="8" t="str"/>
-      <x:c r="G46" s="8" t="str"/>
+      <x:c r="E46" s="8"/>
+      <x:c r="F46" s="8"/>
+      <x:c r="G46" s="8"/>
       <x:c r="H46" s="8" t="str">
         <x:v>Buscar todos los modelos/librerías que usan los CPN afectados. Registrar versión antes/después, guardar el cambio y validar cada librería impactada con muestra permitida y no permitida.</x:v>
       </x:c>
-      <x:c r="I46" s="8" t="str"/>
+      <x:c r="I46" s="8"/>
       <x:c r="J46" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4214,13 +3607,13 @@
       <x:c r="D47" s="8" t="str">
         <x:v>73-104532-01</x:v>
       </x:c>
-      <x:c r="E47" s="8" t="str"/>
-      <x:c r="F47" s="8" t="str"/>
-      <x:c r="G47" s="8" t="str"/>
+      <x:c r="E47" s="8"/>
+      <x:c r="F47" s="8"/>
+      <x:c r="G47" s="8"/>
       <x:c r="H47" s="8" t="str">
         <x:v>En la siguiente corrida tras cambio de modelo/línea, verificar que la librería cargada coincide con la revisión aprobada y repetir el reto OCV/OCR.</x:v>
       </x:c>
-      <x:c r="I47" s="8" t="str"/>
+      <x:c r="I47" s="8"/>
       <x:c r="J47" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4247,13 +3640,13 @@
       <x:c r="D48" s="8" t="str">
         <x:v>73-104532-01</x:v>
       </x:c>
-      <x:c r="E48" s="8" t="str"/>
-      <x:c r="F48" s="8" t="str"/>
-      <x:c r="G48" s="8" t="str"/>
+      <x:c r="E48" s="8"/>
+      <x:c r="F48" s="8"/>
+      <x:c r="G48" s="8"/>
       <x:c r="H48" s="8" t="str">
         <x:v>Revisar logs, usuarios, timestamps y revisiones para demostrar dónde se guardó o no se propagó el cambio. Usar esa evidencia en el RCCA de recurrencia.</x:v>
       </x:c>
-      <x:c r="I48" s="8" t="str"/>
+      <x:c r="I48" s="8"/>
       <x:c r="J48" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4280,13 +3673,13 @@
       <x:c r="D49" s="8" t="str">
         <x:v>73-102022-02</x:v>
       </x:c>
-      <x:c r="E49" s="8" t="str"/>
-      <x:c r="F49" s="8" t="str"/>
-      <x:c r="G49" s="8" t="str"/>
+      <x:c r="E49" s="8"/>
+      <x:c r="F49" s="8"/>
+      <x:c r="G49" s="8"/>
       <x:c r="H49" s="8" t="str">
         <x:v>Actualizar el método de verificación de S1: accionamiento controlado según WI, sin pinza puntiaguda ni empuje lateral. Registrar condición antes y después de intervenir.</x:v>
       </x:c>
-      <x:c r="I49" s="8" t="str"/>
+      <x:c r="I49" s="8"/>
       <x:c r="J49" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4313,13 +3706,13 @@
       <x:c r="D50" s="8" t="str">
         <x:v>73-102022-02</x:v>
       </x:c>
-      <x:c r="E50" s="8" t="str"/>
-      <x:c r="F50" s="8" t="str"/>
-      <x:c r="G50" s="8" t="str"/>
+      <x:c r="E50" s="8"/>
+      <x:c r="F50" s="8"/>
+      <x:c r="G50" s="8"/>
       <x:c r="H50" s="8" t="str">
         <x:v>Revisar alineación, altura/recorrido, contacto y desgaste del actuador de test. Validar repetibilidad del accionamiento sin sobrecarga ni fuerza lateral.</x:v>
       </x:c>
-      <x:c r="I50" s="8" t="str"/>
+      <x:c r="I50" s="8"/>
       <x:c r="J50" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4343,14 +3736,14 @@
       <x:c r="C51" s="8" t="str">
         <x:v>CVEBU</x:v>
       </x:c>
-      <x:c r="D51" s="8" t="str"/>
-      <x:c r="E51" s="8" t="str"/>
-      <x:c r="F51" s="8" t="str"/>
-      <x:c r="G51" s="8" t="str"/>
+      <x:c r="D51" s="8"/>
+      <x:c r="E51" s="8"/>
+      <x:c r="F51" s="8"/>
+      <x:c r="G51" s="8"/>
       <x:c r="H51" s="8" t="str">
         <x:v>Instrumentar cuerpo y terminal/pad de S1, punto de retrabajo y zona de referencia. Registrar temperatura pico, tiempo y ciclos con el mismo retrabajo normalizado por producto.</x:v>
       </x:c>
-      <x:c r="I51" s="8" t="str"/>
+      <x:c r="I51" s="8"/>
       <x:c r="J51" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4374,14 +3767,14 @@
       <x:c r="C52" s="8" t="str">
         <x:v>CVEBU</x:v>
       </x:c>
-      <x:c r="D52" s="8" t="str"/>
-      <x:c r="E52" s="8" t="str"/>
-      <x:c r="F52" s="8" t="str"/>
-      <x:c r="G52" s="8" t="str"/>
+      <x:c r="D52" s="8"/>
+      <x:c r="E52" s="8"/>
+      <x:c r="F52" s="8"/>
+      <x:c r="G52" s="8"/>
       <x:c r="H52" s="8" t="str">
         <x:v>Revisar CAD/Gerber para identificar planos, vías y caminos de cobre entre zonas de retrabajo y S1. Comparar puntos a distancia similar con conectividad térmica diferente.</x:v>
       </x:c>
-      <x:c r="I52" s="8" t="str"/>
+      <x:c r="I52" s="8"/>
       <x:c r="J52" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4405,14 +3798,14 @@
       <x:c r="C53" s="8" t="str">
         <x:v>CVEBU</x:v>
       </x:c>
-      <x:c r="D53" s="8" t="str"/>
-      <x:c r="E53" s="8" t="str"/>
-      <x:c r="F53" s="8" t="str"/>
-      <x:c r="G53" s="8" t="str"/>
+      <x:c r="D53" s="8"/>
+      <x:c r="E53" s="8"/>
+      <x:c r="F53" s="8"/>
+      <x:c r="G53" s="8"/>
       <x:c r="H53" s="8" t="str">
         <x:v>Medir fuerza, recorrido y retorno antes y después de ciclos térmicos controlados, separando calor, contaminación y método de accionamiento.</x:v>
       </x:c>
-      <x:c r="I53" s="8" t="str"/>
+      <x:c r="I53" s="8"/>
       <x:c r="J53" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4436,14 +3829,14 @@
       <x:c r="C54" s="8" t="str">
         <x:v>LANCER</x:v>
       </x:c>
-      <x:c r="D54" s="8" t="str"/>
-      <x:c r="E54" s="8" t="str"/>
-      <x:c r="F54" s="8" t="str"/>
-      <x:c r="G54" s="8" t="str"/>
+      <x:c r="D54" s="8"/>
+      <x:c r="E54" s="8"/>
+      <x:c r="F54" s="8"/>
+      <x:c r="G54" s="8"/>
       <x:c r="H54" s="8" t="str">
         <x:v>Consolidar población con evidencia pre-ICT/post-ICT por serial, WO, lote/date code, estación previa y RefDes. Separar unidades nunca probadas en ICT.</x:v>
       </x:c>
-      <x:c r="I54" s="8" t="str"/>
+      <x:c r="I54" s="8"/>
       <x:c r="J54" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4467,14 +3860,14 @@
       <x:c r="C55" s="8" t="str">
         <x:v>LANCER</x:v>
       </x:c>
-      <x:c r="D55" s="8" t="str"/>
-      <x:c r="E55" s="8" t="str"/>
-      <x:c r="F55" s="8" t="str"/>
-      <x:c r="G55" s="8" t="str"/>
+      <x:c r="D55" s="8"/>
+      <x:c r="E55" s="8"/>
+      <x:c r="F55" s="8"/>
+      <x:c r="G55" s="8"/>
       <x:c r="H55" s="8" t="str">
         <x:v>Comparar referencias QSFP falladas con referencias sanas del mismo PN. Revisar SMT/reflow, historial de manejo/retrabajo y exposiciones eléctricas anteriores a ICT.</x:v>
       </x:c>
-      <x:c r="I55" s="8" t="str"/>
+      <x:c r="I55" s="8"/>
       <x:c r="J55" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4498,14 +3891,14 @@
       <x:c r="C56" s="8" t="str">
         <x:v>LANCER</x:v>
       </x:c>
-      <x:c r="D56" s="8" t="str"/>
-      <x:c r="E56" s="8" t="str"/>
-      <x:c r="F56" s="8" t="str"/>
-      <x:c r="G56" s="8" t="str"/>
+      <x:c r="D56" s="8"/>
+      <x:c r="E56" s="8"/>
+      <x:c r="F56" s="8"/>
+      <x:c r="G56" s="8"/>
       <x:c r="H56" s="8" t="str">
         <x:v>Actualizar la investigación y comunicación con la evidencia pre-ICT. Retirar ICT como causa iniciadora de toda la población y mantener abierto el mecanismo de degradación.</x:v>
       </x:c>
-      <x:c r="I56" s="8" t="str"/>
+      <x:c r="I56" s="8"/>
       <x:c r="J56" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4532,17 +3925,17 @@
       <x:c r="D57" s="8" t="str">
         <x:v>73-103083-04</x:v>
       </x:c>
-      <x:c r="E57" s="8" t="str"/>
-      <x:c r="F57" s="8" t="str"/>
-      <x:c r="G57" s="8" t="str"/>
+      <x:c r="E57" s="8"/>
+      <x:c r="F57" s="8"/>
+      <x:c r="G57" s="8"/>
       <x:c r="H57" s="8" t="str">
         <x:v>Implementar inspección 100 % post-PTH de los conectores afectados. Ante el primer puente, detener, segregar desde el último serial bueno y registrar alcance por WO/serial.</x:v>
       </x:c>
-      <x:c r="I57" s="8" t="str"/>
+      <x:c r="I57" s="8"/>
       <x:c r="J57" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K57" s="8" t="str"/>
+      <x:c r="K57" s="8"/>
       <x:c r="L57" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: Lista de población y resultados por serial; última unidad buena identificada y autorización de reinicio documentada.</x:v>
       </x:c>
@@ -4563,17 +3956,17 @@
       <x:c r="D58" s="8" t="str">
         <x:v>73-103083-04</x:v>
       </x:c>
-      <x:c r="E58" s="8" t="str"/>
-      <x:c r="F58" s="8" t="str"/>
-      <x:c r="G58" s="8" t="str"/>
+      <x:c r="E58" s="8"/>
+      <x:c r="F58" s="8"/>
+      <x:c r="G58" s="8"/>
       <x:c r="H58" s="8" t="str">
         <x:v>Revisar receta, flux, preheat, conveyor, ola, pallet y terminales. Comparar condiciones de unidades con y sin puentes y validar el cambio seleccionado.</x:v>
       </x:c>
-      <x:c r="I58" s="8" t="str"/>
+      <x:c r="I58" s="8"/>
       <x:c r="J58" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K58" s="8" t="str"/>
+      <x:c r="K58" s="8"/>
       <x:c r="L58" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: Comparativo y corrida controlada que sustenten el mecanismo y efectividad del control.</x:v>
       </x:c>
@@ -4588,21 +3981,21 @@
       <x:c r="B59" s="8" t="str">
         <x:v>LL-TTM-TDR-RAYONES</x:v>
       </x:c>
-      <x:c r="C59" s="8" t="str"/>
+      <x:c r="C59" s="8"/>
       <x:c r="D59" s="8" t="str">
         <x:v>28-14458-04</x:v>
       </x:c>
-      <x:c r="E59" s="8" t="str"/>
-      <x:c r="F59" s="8" t="str"/>
-      <x:c r="G59" s="8" t="str"/>
+      <x:c r="E59" s="8"/>
+      <x:c r="F59" s="8"/>
+      <x:c r="G59" s="8"/>
       <x:c r="H59" s="8" t="str">
         <x:v>Implementar separación con film y método de manejo que evite contacto/roce en cupones durante descarga AOI. Revisar punto físico de generación del rayón.</x:v>
       </x:c>
-      <x:c r="I59" s="8" t="str"/>
+      <x:c r="I59" s="8"/>
       <x:c r="J59" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K59" s="8" t="str"/>
+      <x:c r="K59" s="8"/>
       <x:c r="L59" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: WI/método aprobado y evidencia de descarga sin rayones en validación.</x:v>
       </x:c>
@@ -4617,21 +4010,21 @@
       <x:c r="B60" s="8" t="str">
         <x:v>LL-TTM-TDR-RAYONES</x:v>
       </x:c>
-      <x:c r="C60" s="8" t="str"/>
+      <x:c r="C60" s="8"/>
       <x:c r="D60" s="8" t="str">
         <x:v>28-14458-04</x:v>
       </x:c>
-      <x:c r="E60" s="8" t="str"/>
-      <x:c r="F60" s="8" t="str"/>
-      <x:c r="G60" s="8" t="str"/>
+      <x:c r="E60" s="8"/>
+      <x:c r="F60" s="8"/>
+      <x:c r="G60" s="8"/>
       <x:c r="H60" s="8" t="str">
         <x:v>Conciliar resultados TDR, condición de cupones y alcance del daño. Registrar lote, date code, cantidad, embarque y aceptación específica del cliente antes de liberar la población.</x:v>
       </x:c>
-      <x:c r="I60" s="8" t="str"/>
+      <x:c r="I60" s="8"/>
       <x:c r="J60" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K60" s="8" t="str"/>
+      <x:c r="K60" s="8"/>
       <x:c r="L60" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: Disposición aprobada de la población exacta, trazabilidad y resolución de discrepancias del reporte.</x:v>
       </x:c>
@@ -4646,21 +4039,21 @@
       <x:c r="B61" s="8" t="str">
         <x:v>LL-731991908-LAVADO-REIMPRESION</x:v>
       </x:c>
-      <x:c r="C61" s="8" t="str"/>
+      <x:c r="C61" s="8"/>
       <x:c r="D61" s="8" t="str">
         <x:v>73-19919-08</x:v>
       </x:c>
-      <x:c r="E61" s="8" t="str"/>
-      <x:c r="F61" s="8" t="str"/>
-      <x:c r="G61" s="8" t="str"/>
+      <x:c r="E61" s="8"/>
+      <x:c r="F61" s="8"/>
+      <x:c r="G61" s="8"/>
       <x:c r="H61" s="8" t="str">
         <x:v>Reforzar la ruta de lavado aprobada para PCBs con impresión rechazada y verificar limpieza antes de reimpresión. Evitar sustituir lavadora por limpieza manual no autorizada.</x:v>
       </x:c>
-      <x:c r="I61" s="8" t="str"/>
+      <x:c r="I61" s="8"/>
       <x:c r="J61" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K61" s="8" t="str"/>
+      <x:c r="K61" s="8"/>
       <x:c r="L61" s="8" t="str">
         <x:v>Acción documentada. Cierre sin confirmar. Para cerrar: Registros de lavado/verificación y cumplimiento de WI en la siguiente corrida aplicable.</x:v>
       </x:c>
@@ -4675,21 +4068,21 @@
       <x:c r="B62" s="8" t="str">
         <x:v>LL-731991908-LAVADO-REIMPRESION</x:v>
       </x:c>
-      <x:c r="C62" s="8" t="str"/>
+      <x:c r="C62" s="8"/>
       <x:c r="D62" s="8" t="str">
         <x:v>73-19919-08</x:v>
       </x:c>
-      <x:c r="E62" s="8" t="str"/>
-      <x:c r="F62" s="8" t="str"/>
-      <x:c r="G62" s="8" t="str"/>
+      <x:c r="E62" s="8"/>
+      <x:c r="F62" s="8"/>
+      <x:c r="G62" s="8"/>
       <x:c r="H62" s="8" t="str">
         <x:v>Crear buffer identificado y control de trazabilidad para separar PCBs pendientes de lavado, limpias y autorizadas para reimpresión.</x:v>
       </x:c>
-      <x:c r="I62" s="8" t="str"/>
+      <x:c r="I62" s="8"/>
       <x:c r="J62" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K62" s="8" t="str"/>
+      <x:c r="K62" s="8"/>
       <x:c r="L62" s="8" t="str">
         <x:v>Acción documentada. Cierre sin confirmar. Para cerrar: Separación física y registro que impidan regresar una unidad pendiente de lavado a impresora.</x:v>
       </x:c>
@@ -4704,21 +4097,21 @@
       <x:c r="B63" s="8" t="str">
         <x:v>LL-731991908-LAVADO-REIMPRESION</x:v>
       </x:c>
-      <x:c r="C63" s="8" t="str"/>
+      <x:c r="C63" s="8"/>
       <x:c r="D63" s="8" t="str">
         <x:v>73-19919-08</x:v>
       </x:c>
-      <x:c r="E63" s="8" t="str"/>
-      <x:c r="F63" s="8" t="str"/>
-      <x:c r="G63" s="8" t="str"/>
+      <x:c r="E63" s="8"/>
+      <x:c r="F63" s="8"/>
+      <x:c r="G63" s="8"/>
       <x:c r="H63" s="8" t="str">
         <x:v>Entrenar en Stop, Call and Wait ante impresión repetidamente rechazada. Conciliar población afectada y verificar efectividad en la siguiente corrida.</x:v>
       </x:c>
-      <x:c r="I63" s="8" t="str"/>
+      <x:c r="I63" s="8"/>
       <x:c r="J63" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K63" s="8" t="str"/>
+      <x:c r="K63" s="8"/>
       <x:c r="L63" s="8" t="str">
         <x:v>Acción documentada. Cierre sin confirmar. Para cerrar: Entrenamiento y auditoría de ruta; conteos por estación reconciliados, sin repetir residuos/cortos asociados.</x:v>
       </x:c>
@@ -4733,19 +4126,19 @@
       <x:c r="B64" s="8" t="str">
         <x:v>LL-PRESSFIT-CENTRADO</x:v>
       </x:c>
-      <x:c r="C64" s="8" t="str"/>
-      <x:c r="D64" s="8" t="str"/>
-      <x:c r="E64" s="8" t="str"/>
-      <x:c r="F64" s="8" t="str"/>
-      <x:c r="G64" s="8" t="str"/>
+      <x:c r="C64" s="8"/>
+      <x:c r="D64" s="8"/>
+      <x:c r="E64" s="8"/>
+      <x:c r="F64" s="8"/>
+      <x:c r="G64" s="8"/>
       <x:c r="H64" s="8" t="str">
         <x:v>Implementar y validar láser/referencia de centrado para el fixture, verificando soporte, paralelismo y contacto uniforme bajo el dado.</x:v>
       </x:c>
-      <x:c r="I64" s="8" t="str"/>
+      <x:c r="I64" s="8"/>
       <x:c r="J64" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K64" s="8" t="str"/>
+      <x:c r="K64" s="8"/>
       <x:c r="L64" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: Producto y fixture identificados, alineación controlada y evidencia de distribución/asentamiento conforme.</x:v>
       </x:c>
@@ -4760,19 +4153,19 @@
       <x:c r="B65" s="8" t="str">
         <x:v>LL-PRESSFIT-CENTRADO</x:v>
       </x:c>
-      <x:c r="C65" s="8" t="str"/>
-      <x:c r="D65" s="8" t="str"/>
-      <x:c r="E65" s="8" t="str"/>
-      <x:c r="F65" s="8" t="str"/>
-      <x:c r="G65" s="8" t="str"/>
+      <x:c r="C65" s="8"/>
+      <x:c r="D65" s="8"/>
+      <x:c r="E65" s="8"/>
+      <x:c r="F65" s="8"/>
+      <x:c r="G65" s="8"/>
       <x:c r="H65" s="8" t="str">
         <x:v>Validar gage post-pressfit para medir seating/gap según drawing aprobado. Definir en WI reacción ante pins elevados o asentamiento incompleto.</x:v>
       </x:c>
-      <x:c r="I65" s="8" t="str"/>
+      <x:c r="I65" s="8"/>
       <x:c r="J65" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K65" s="8" t="str"/>
+      <x:c r="K65" s="8"/>
       <x:c r="L65" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: Gage y criterio aprobados con muestras conformes/no conformes; discrepancias dimensionales resueltas.</x:v>
       </x:c>
@@ -4787,19 +4180,19 @@
       <x:c r="B66" s="8" t="str">
         <x:v>LL-PRESSFIT-CENTRADO</x:v>
       </x:c>
-      <x:c r="C66" s="8" t="str"/>
-      <x:c r="D66" s="8" t="str"/>
-      <x:c r="E66" s="8" t="str"/>
-      <x:c r="F66" s="8" t="str"/>
-      <x:c r="G66" s="8" t="str"/>
+      <x:c r="C66" s="8"/>
+      <x:c r="D66" s="8"/>
+      <x:c r="E66" s="8"/>
+      <x:c r="F66" s="8"/>
+      <x:c r="G66" s="8"/>
       <x:c r="H66" s="8" t="str">
         <x:v>Cotejar registros de las 100 PCBA reportadas con VI/5DX/PCBFT y el plan AOI 20 %. Confirmar qué controles quedaron instalados y cuáles siguen propuestos.</x:v>
       </x:c>
-      <x:c r="I66" s="8" t="str"/>
+      <x:c r="I66" s="8"/>
       <x:c r="J66" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="K66" s="8" t="str"/>
+      <x:c r="K66" s="8"/>
       <x:c r="L66" s="8" t="str">
         <x:v>Propuesta documentada. Ejecución y cierre sin confirmar. Para cerrar: Reporte por población/prueba y evidencia del control permanente; no cerrar láser por el resultado de contención.</x:v>
       </x:c>
@@ -4817,14 +4210,14 @@
       <x:c r="C67" s="8" t="str">
         <x:v>NIXIE</x:v>
       </x:c>
-      <x:c r="D67" s="8" t="str"/>
-      <x:c r="E67" s="8" t="str"/>
-      <x:c r="F67" s="8" t="str"/>
-      <x:c r="G67" s="8" t="str"/>
+      <x:c r="D67" s="8"/>
+      <x:c r="E67" s="8"/>
+      <x:c r="F67" s="8"/>
+      <x:c r="G67" s="8"/>
       <x:c r="H67" s="8" t="str">
         <x:v>Ejecutar DOE de geometrías de aperturas del aro discutidas: comparar stencil actual de 3 gajos con alternativas segmentadas/semiabiertas, manteniendo criterios de voids y volumen. No adoptar ring completo solo para eliminar beads.</x:v>
       </x:c>
-      <x:c r="I67" s="8" t="str"/>
+      <x:c r="I67" s="8"/>
       <x:c r="J67" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4848,14 +4241,14 @@
       <x:c r="C68" s="8" t="str">
         <x:v>NIXIE</x:v>
       </x:c>
-      <x:c r="D68" s="8" t="str"/>
-      <x:c r="E68" s="8" t="str"/>
-      <x:c r="F68" s="8" t="str"/>
-      <x:c r="G68" s="8" t="str"/>
+      <x:c r="D68" s="8"/>
+      <x:c r="E68" s="8"/>
+      <x:c r="F68" s="8"/>
+      <x:c r="G68" s="8"/>
       <x:c r="H68" s="8" t="str">
         <x:v>Correlacionar RX de bead/tilt/voids y coplanaridad con sensibilidad dBFS a 94 dBSPL y respuesta a 1/3.15/10 kHz, según límites aprobados para el producto.</x:v>
       </x:c>
-      <x:c r="I68" s="8" t="str"/>
+      <x:c r="I68" s="8"/>
       <x:c r="J68" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4879,14 +4272,14 @@
       <x:c r="C69" s="8" t="str">
         <x:v>NIXIE</x:v>
       </x:c>
-      <x:c r="D69" s="8" t="str"/>
-      <x:c r="E69" s="8" t="str"/>
-      <x:c r="F69" s="8" t="str"/>
-      <x:c r="G69" s="8" t="str"/>
+      <x:c r="D69" s="8"/>
+      <x:c r="E69" s="8"/>
+      <x:c r="F69" s="8"/>
+      <x:c r="G69" s="8"/>
       <x:c r="H69" s="8" t="str">
         <x:v>Actualizar WI/PFMEA/Control Plan con los límites y método de inspección/prueba validados tras DOE. Incorporar reacción ante levantamiento y pérdida acústica.</x:v>
       </x:c>
-      <x:c r="I69" s="8" t="str"/>
+      <x:c r="I69" s="8"/>
       <x:c r="J69" s="8" t="str">
         <x:v>Open</x:v>
       </x:c>
@@ -4899,11 +4292,41 @@
       <x:c r="M69" s="8" t="str">
         <x:v>Y</x:v>
       </x:c>
+    </x:row>
+    <x:row r="70" ht="105" customHeight="1">
+      <x:c r="A70" s="9"/>
+      <x:c r="B70" s="9"/>
+      <x:c r="C70" s="9"/>
+      <x:c r="D70" s="9"/>
+      <x:c r="E70" s="9"/>
+      <x:c r="F70" s="9"/>
+      <x:c r="G70" s="9"/>
+      <x:c r="H70" s="9"/>
+      <x:c r="I70" s="9"/>
+      <x:c r="J70" s="9"/>
+      <x:c r="K70" s="9"/>
+      <x:c r="L70" s="9"/>
+      <x:c r="M70" s="9"/>
+    </x:row>
+    <x:row r="71" ht="105" customHeight="1">
+      <x:c r="A71" s="9"/>
+      <x:c r="B71" s="9"/>
+      <x:c r="C71" s="9"/>
+      <x:c r="D71" s="9"/>
+      <x:c r="E71" s="9"/>
+      <x:c r="F71" s="9"/>
+      <x:c r="G71" s="9"/>
+      <x:c r="H71" s="9"/>
+      <x:c r="I71" s="9"/>
+      <x:c r="J71" s="9"/>
+      <x:c r="K71" s="9"/>
+      <x:c r="L71" s="9"/>
+      <x:c r="M71" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R233b09a604f049dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60141b7687294392"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5902,7 +5325,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10fda3c7a3ce41cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R369fce84575043e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6455,7 +5878,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc556aa22048f41d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f5cd51a03284b1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6587,7 +6010,7 @@
         </x:is>
       </x:c>
       <x:c r="B12" s="2" t="str">
-        <x:v>Agregar solo lecciones y acciones documentadas. No suponer causa, responsable, fecha, cierre ni alcance.</x:v>
+        <x:v>Agregar nuevos eventos solo con cierre documentado, análisis respaldado por evidencia y conclusión validada. No agregar investigaciones abiertas, hipótesis ni acciones propuestas. No suponer causa, responsable, fecha, cierre ni alcance.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="29" customHeight="1">
@@ -6693,7 +6116,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc47db1e791d84dac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf7dfaf8ec5f4b22"/>
   </x:tableParts>
 </x:worksheet>
 </file>